--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bengrier/Desktop/CSU Work/AI App Creation/Office Hours Display/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bengrier/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAEDD2F-EB34-5B40-B182-65870971DB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9470167C-8304-2447-9874-4B7E090C9D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32020" yWindow="-3960" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="people" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="200">
   <si>
     <t>name</t>
   </si>
@@ -853,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -865,6 +865,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2118,7 +2119,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -2186,7 +2187,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -2424,7 +2425,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>55</v>
       </c>
@@ -2934,18 +2935,18 @@
         <v>92</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>38</v>
       </c>
       <c r="B73" t="s">
-        <v>107</v>
-      </c>
-      <c r="C73" t="s">
-        <v>93</v>
-      </c>
-      <c r="D73" t="s">
-        <v>94</v>
+        <v>89</v>
+      </c>
+      <c r="C73" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="D73" s="6">
+        <v>0.41666666666666669</v>
       </c>
       <c r="E73" t="s">
         <v>92</v>
@@ -3512,7 +3513,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>55</v>
       </c>
@@ -3580,7 +3581,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>38</v>
       </c>
@@ -3597,7 +3598,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>55</v>
       </c>
@@ -3631,7 +3632,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>38</v>
       </c>
@@ -4128,7 +4129,7 @@
   <autoFilter ref="A1:E142" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Prof Scheller"/>
+        <filter val="Lauren Watts"/>
       </filters>
     </filterColumn>
   </autoFilter>
